--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0116.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0116.xlsx
@@ -11039,7 +11039,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Để ta lo. Ta làm việc này bao năm rồi. Còn lo ta không xử lý nổi à?</t>
+          <t>Để tao lo. Tao làm việc này bao năm rồi. Còn lo tao không xử lý nổi à?</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Luke, sẵn sàng chưa? Hôm nay cậu phải chạy thêm hai chuyến nữa đấy.</t>
+          <t>Luke, sẵn sàng chưa? Hôm nay mày phải chạy thêm hai chuyến nữa đấy.</t>
         </is>
       </c>
     </row>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>(Nếu ta không nhầm… những cái tên trong danh sách này rất có thể là gián điệp của Outcasts đang hoạt động trong Spacetrek Collective.)</t>
+          <t>(Nếu tao không nhầm… những cái tên trong danh sách này rất có thể là gián điệp của Outcasts đang hoạt động trong Spacetrek Collective.)</t>
         </is>
       </c>
     </row>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Ta vừa phát hiện một danh sách chưa hoàn chỉnh của Spacetrek Collective. Những người trong đó chắc chắn đã bị mua chuộc hoặc đe dọa bởi bọn Outcasts. Chúng là gián điệp.</t>
+          <t>Tao vừa phát hiện một danh sách chưa hoàn chỉnh của Spacetrek Collective. Những người trong đó chắc chắn đã bị mua chuộc hoặc đe dọa bởi bọn Outcasts. Chúng là gián điệp.</t>
         </is>
       </c>
     </row>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Ta có mấy món đồ hiếm ở đây, rất hợp cho một lữ khách như cậu sau chuyến đi xa như vậy.</t>
+          <t>Tao có mấy món đồ hiếm ở đây, rất hợp cho một lữ khách như cậu sau chuyến đi xa như vậy.</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Thật ra ta hay lui tới chợ lắm. À mà nói đến chợ, mấy lái buôn thường tụ tập ở đó hết…</t>
+          <t>Thật ra tao hay lui tới chợ lắm. À mà nói đến chợ, mấy lái buôn thường tụ tập ở đó hết…</t>
         </is>
       </c>
     </row>
@@ -14029,7 +14029,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Để ta lo. Ta làm việc này bao năm rồi. Còn lo ta không xử lý nổi à?</t>
+          <t>Để tao lo. Tao làm việc này bao năm rồi. Còn lo tao không xử lý nổi à?</t>
         </is>
       </c>
     </row>
@@ -15329,7 +15329,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Ý bạn là gì?</t>
+          <t>Ý anh là sao?</t>
         </is>
       </c>
     </row>
@@ -15394,7 +15394,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Hê! Ý ta là... muốn có đồ xịn thì phải tìm đúng nguồn hàng thôi.</t>
+          <t>Hê! Ý tao là... muốn có đồ xịn thì phải tìm đúng nguồn hàng thôi.</t>
         </is>
       </c>
     </row>
@@ -15784,7 +15784,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Ý bạn là gì?</t>
+          <t>Ý anh là sao?</t>
         </is>
       </c>
     </row>
@@ -15849,7 +15849,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Hê! Ý ta là... muốn có đồ xịn thì phải tìm đúng nguồn hàng thôi.</t>
+          <t>Hê! Ý tao là... muốn có đồ xịn thì phải tìm đúng nguồn hàng thôi.</t>
         </is>
       </c>
     </row>
@@ -16369,7 +16369,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Nếu cậu muốn tiền... để ta suy nghĩ đã.</t>
+          <t>Nếu cậu muốn tiền... để tao suy nghĩ đã.</t>
         </is>
       </c>
     </row>
@@ -16759,7 +16759,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Ngươi chắc kết nối được cho ta à? Vậy sao ta chưa nghe tên ngươi bao giờ? Đừng có bịa chuyện nhé?</t>
+          <t>Mày chắc kết nối được cho tao à? Vậy sao tao chưa nghe tên mày bao giờ? Đừng có bịa chuyện nhé?</t>
         </is>
       </c>
     </row>
@@ -16889,7 +16889,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Tin ta hay không... Tùy cậu thôi.</t>
+          <t>Tin tao hay không... Tùy cậu thôi.</t>
         </is>
       </c>
     </row>
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Đừng có mà quay lại cầu xin ta sau này, khi đã hối hận vì quyết định của mình. Đến lúc đó, cơ hội vàng như thế này sẽ không còn đâu.</t>
+          <t>Đừng có mà quay lại cầu xin tao sau này, khi đã hối hận vì quyết định của mình. Đến lúc đó, cơ hội vàng như thế này sẽ không còn đâu.</t>
         </is>
       </c>
     </row>
@@ -18189,7 +18189,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Đồ mà ta không tìm được à?</t>
+          <t>Đồ mà tao không tìm được à?</t>
         </is>
       </c>
     </row>
@@ -18254,7 +18254,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Đồ mà ta không mua được à?</t>
+          <t>Đồ mà tao không mua được à?</t>
         </is>
       </c>
     </row>
@@ -18579,7 +18579,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Haha! Ngươi đến đúng lúc đấy. Nhưng... Người bảo lãnh của ngươi đâu? Chúng ta không giao dịch với kẻ lạ mặt đâu.</t>
+          <t>Haha! Mày đến đúng lúc đấy. Nhưng... Người bảo lãnh của mày đâu? Chúng tao không giao dịch với kẻ lạ mặt đâu.</t>
         </is>
       </c>
     </row>
@@ -19229,7 +19229,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Nhưng theo ta thì ông chủ chỉ đang lo quá mức thôi. Chẳng phải đây là chuyện thường ngày của tụi mình sao, có gì mà phải lo lắng chứ?</t>
+          <t>Nhưng theo tao thì ông chủ chỉ đang lo quá mức thôi. Chẳng phải đây là chuyện thường ngày của tụi mình sao, có gì mà phải lo lắng chứ?</t>
         </is>
       </c>
     </row>
@@ -19359,7 +19359,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Tch… Được rồi, thấy ngươi cũng thẳng tính, ta sẽ mách cho một bí mật.</t>
+          <t>Tch… Được rồi, thấy mày cũng thẳng tính, tao sẽ mách cho một bí mật.</t>
         </is>
       </c>
     </row>
@@ -19424,7 +19424,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Tìm thương nhân tên Sonam ở Trạm Trung Chuyển. Ta sẽ giao dịch với hắn khi hắn đồng ý làm nhà tài trợ cho ngươi.</t>
+          <t>Tìm thương nhân tên Sonam ở Trạm Trung Chuyển. Tao sẽ giao dịch với hắn khi hắn đồng ý làm nhà tài trợ cho mày.</t>
         </is>
       </c>
     </row>
@@ -19554,7 +19554,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Đi đi! Biến đi! Không thấy ta đang bận à?!</t>
+          <t>Đi đi! Biến đi! Không thấy tao đang bận à?!</t>
         </is>
       </c>
     </row>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Đưa nhà tài trợ của ngươi đến đây. Nếu muốn làm ăn, ta phải nghe nhà tài trợ của ngươi nói trước đã.</t>
+          <t>Đưa nhà tài trợ của mày đến đây. Nếu muốn làm ăn, tao phải nghe nhà tài trợ của mày nói trước đã.</t>
         </is>
       </c>
     </row>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Ta muốn ngươi có mặt ở đây đúng giờ. Chỉ cần tuân thủ luật chơi và đừng gây rắc rối là được.</t>
+          <t>Tao muốn mày có mặt ở đây đúng giờ. Chỉ cần tuân thủ luật chơi và đừng gây rắc rối là được.</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Đừng có giả nai với ta.</t>
+          <t>Đừng có giả nai với tao.</t>
         </is>
       </c>
     </row>
@@ -20659,7 +20659,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Kết nối hả? Ta chẳng cho ngươi biết cái quái gì đâu, nghe chưa?</t>
+          <t>Kết nối hả? Tao chẳng cho mày biết cái quái gì đâu, nghe chưa?</t>
         </is>
       </c>
     </row>
@@ -20789,7 +20789,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Haha! Ngươi nói cũng có lý. Ta không tin ngươi dám gây chuyện đâu.</t>
+          <t>Haha! Mày nói cũng có lý. Tao không tin mày dám gây chuyện đâu.</t>
         </is>
       </c>
     </row>
@@ -21179,7 +21179,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Đừng có giả nai với ta.</t>
+          <t>Đừng có giả nai với tao.</t>
         </is>
       </c>
     </row>
@@ -21634,7 +21634,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Kết nối hả? Ta chẳng cho ngươi biết cái quái gì đâu, nghe chưa?</t>
+          <t>Kết nối hả? Tao chẳng cho mày biết cái quái gì đâu, nghe chưa?</t>
         </is>
       </c>
     </row>
@@ -21764,7 +21764,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Haha! Ngươi nói cũng có lý. Ta không tin ngươi dám gây chuyện đâu.</t>
+          <t>Haha! Mày nói cũng có lý. Tao không tin mày dám gây chuyện đâu.</t>
         </is>
       </c>
     </row>
@@ -22609,7 +22609,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Brax đã giới thiệu cậu với cậu đấy.</t>
+          <t>Brax đã giới thiệu cậu với mày đấy.</t>
         </is>
       </c>
     </row>
@@ -22804,7 +22804,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Nhưng quy tắc là quy tắc. Nếu cậu muốn ta làm người bảo trợ cho cậu, thì cậu phải thể hiện "thành ý" đi.</t>
+          <t>Nhưng quy tắc là quy tắc. Nếu cậu muốn tao làm người bảo trợ cho cậu, thì cậu phải thể hiện "thành ý" đi.</t>
         </is>
       </c>
     </row>
@@ -22869,7 +22869,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Nếu cậu muốn tiền... để ta suy nghĩ đã.</t>
+          <t>Nếu cậu muốn tiền... để tao suy nghĩ đã.</t>
         </is>
       </c>
     </row>
@@ -23129,7 +23129,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Thỏa thuận thế là xong.</t>
+          <t>Thỏa thuận rồi đấy.</t>
         </is>
       </c>
     </row>
@@ -24169,7 +24169,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Đủ rồi đấy. Nếu trả tiền thì qua bên trái. Nếu chỉ xem thì qua bên phải. Còn không có tiền thì r?i ?i.</t>
+          <t>Đủ rồi đấy. Nếu trả tiền thì qua bên trái. Nếu chỉ xem thì qua bên phải. Còn không có tiền thì cút đi.</t>
         </is>
       </c>
     </row>
@@ -24299,7 +24299,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Ừ, cậu biết ta đã phải trả giá bao nhiêu để có mặt ở đây không? Nếu cậu có gì hay ho, đưa ra ngay đi để xem có đáng không.</t>
+          <t>Ừ, cậu biết tao đã phải trả giá bao nhiêu để có mặt ở đây không? Nếu cậu có gì hay ho, đưa ra ngay đi để xem có đáng không.</t>
         </is>
       </c>
     </row>
@@ -24494,7 +24494,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Đưa mấy con &lt;ano=A-grade&gt;"còn sống"&lt;/ano&gt; ra đây.</t>
+          <t>Đưa mấy con &lt;ano=A-grade &gt;"còn sống"&lt;/ano&gt; ra đây.</t>
         </is>
       </c>
     </row>
@@ -25599,7 +25599,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Sau tất cả những gì ta đã trải qua để đến được đây... Ừm... Này, ông bầu, cho ta mượn chút tín dụng được không? Ta sẽ trả lại sau.</t>
+          <t>Sau tất cả những gì tao đã trải qua để đến được đây... Ừm... Này, ông bầu, cho tao mượn chút tín dụng được không? Tao sẽ trả lại sau.</t>
         </is>
       </c>
     </row>
@@ -25989,7 +25989,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Đừng nói là ta không cảnh báo trước nếu cậu gặp rắc rối đấy.</t>
+          <t>Đừng nói là tao không cảnh báo trước nếu cậu gặp rắc rối đấy.</t>
         </is>
       </c>
     </row>
@@ -27549,7 +27549,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Món đồ cuối cùng: 300.000 Tín Dụng Vỏ Sò. Có ai muốn không?</t>
+          <t>Món đồ cuối cùng: 300.000 Shell Credit Sò. Có ai muốn không?</t>
         </is>
       </c>
     </row>
@@ -28524,7 +28524,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Ồ, Sonam à. Khách hàng của cậu đúng là gan dạ khi báo cho Spacetrek Collective. Mà lâu nay ta cứ tưởng ngươi là người của chúng ta cơ đấy.</t>
+          <t>Ồ, Sonam à. Khách hàng của cậu đúng là gan dạ khi báo cho Spacetrek Collective. Mà lâu nay tao cứ tưởng mày là người của chúng tao cơ đấy.</t>
         </is>
       </c>
     </row>
@@ -28654,7 +28654,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Ta thấy rồi! Chính {Male=hắn;Female=cô ta} ấy! {Male=Hắn;Female:Cô ta} đã lảng vảng quanh trại lúc nãy!</t>
+          <t>Ta thấy rồi! Chính {Male=He;Female=She} ấy! {Male=He;Female=She} đã lảng vảng quanh trại lúc nãy!</t>
         </is>
       </c>
     </row>
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Lôi {Male=hắn;Female=nó} lại đây cho ta! Và dọn sạch chỗ này trước khi họ tới!</t>
+          <t>Lôi {Male=him;Female=her} lại đây cho tao! Và dọn sạch chỗ này trước khi họ tới!</t>
         </is>
       </c>
     </row>
@@ -29109,7 +29109,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Món đồ cuối cùng: 300.000 Tín Dụng Vỏ Sò. Có ai muốn không?</t>
+          <t>Món đồ cuối cùng: 300.000 Shell Credit Sò. Có ai muốn không?</t>
         </is>
       </c>
     </row>
@@ -30084,7 +30084,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Ồ, Sonam à. Khách hàng của cậu đúng là gan dạ khi báo cho Spacetrek Collective. Mà lâu nay ta cứ tưởng ngươi là người của chúng ta cơ đấy.</t>
+          <t>Ồ, Sonam à. Khách hàng của cậu đúng là gan dạ khi báo cho Spacetrek Collective. Mà lâu nay tao cứ tưởng mày là người của chúng tao cơ đấy.</t>
         </is>
       </c>
     </row>
@@ -30214,7 +30214,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Ta thấy rồi! Chính {Male=hắn;Female=cô ta} ấy! {Male=Hắn;Female:Cô ta} đã lảng vảng quanh trại lúc nãy!</t>
+          <t>Ta thấy rồi! Chính {Male=He;Female=She} ấy! {Male=He;Female=She} đã lảng vảng quanh trại lúc nãy!</t>
         </is>
       </c>
     </row>
@@ -30344,7 +30344,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Lôi {Male=hắn;Female=nó} lại đây cho ta! Và dọn sạch chỗ này trước khi họ tới!</t>
+          <t>Lôi {Male=him;Female=her} lại đây cho tao! Và dọn sạch chỗ này trước khi họ tới!</t>
         </is>
       </c>
     </row>
@@ -30669,7 +30669,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Thôi được rồi... Ta thua rồi. Giết hay tra tấn gì thì làm đi, đừng kéo dài nữa.</t>
+          <t>Thôi được rồi... Tao thua rồi. Giết hay tra tấn gì thì làm đi, đừng kéo dài nữa.</t>
         </is>
       </c>
     </row>
